--- a/daily_matches/job_matches_2026-10-02.xlsx
+++ b/daily_matches/job_matches_2026-10-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,147 +456,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca95058df9983f8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Copilot, BigQuery, FastAPI, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67b03e4a412a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
+          <t>Production Bioinformatics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, S3, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1c2a1b4ab40cf7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Software Developer 2)</t>
+          <t>Production Bioinformatics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Docker, Kubernetes, NoSQL, Python, SQL, R, C++</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afac6f1d83728f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2795ba2ac2c023</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Solutions &amp; Implementation Specialist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -606,15 +606,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
+          <t>Data Scientist, Git, Snowflake, Hadoop, MongoDB, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89fab24453b8fee</t>
+          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>Data Scientist, Git, Snowflake, Hadoop, MongoDB, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=274e5a94ddfdccfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d54c452b6b9f10</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Software Engineer - AI Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>RTI International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a3799060fb00b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53c1a4e4aacfb3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend, Level 5</t>
+          <t>Full Stack Engineer 4 (PySpark)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, C++, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PySpark, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,19 +764,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c187da77d375a82d</t>
+          <t>https://www.indeed.com/viewjob?jk=5576f999a81177b2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Priceline.com</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -785,151 +785,151 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Git, SQL, R, Java, Optimization</t>
+          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676fe19cd35a048b</t>
+          <t>https://www.indeed.com/viewjob?jk=12b2ab923ca77b28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Customer Engineer - LATAM</t>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mixpanel</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3cc38f9560c3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=464c9249b43d0e07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Customer Engineer - LATAM</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mixpanel</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947682d4b49857d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ced4fe47a4f1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Customer Engineer - LATAM</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mixpanel</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0322dcdcfe6aba23</t>
+          <t>https://www.indeed.com/viewjob?jk=1979d7025fe17b0e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Enterprise</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,102 +939,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020a04f078ff7218</t>
+          <t>https://www.indeed.com/viewjob?jk=e63f85728fde97d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Security Engineer, Business Continuity &amp; Risk</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25375922af2715b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f8927daa68bfadc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Advisor - Scientific Machine Learning &amp; Agentic Workflows Engineer</t>
+          <t>Senior Backend Developer (AI, Python)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, CI/CD, Git, Python, R, Optimization, Bayesian</t>
+          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5983dd660bdae7</t>
+          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2027 Summer Intern - AI/ML Engineer, Autonomous Vehicle: Simulation</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, Python, R, Java, C++</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346f06e95cddae13</t>
+          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Enterprise Engineering</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CodeRabbit</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2b32a758bff990</t>
+          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI/ML Process Engineering Intern (Spring 2027)</t>
+          <t>Associate Full Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, OpenCV, Python, R, Optimization, Bayesian</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,42 +1114,742 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e85845e6f6f6090</t>
+          <t>https://www.indeed.com/viewjob?jk=938793961653bac4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scientist</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University of Rochester</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2ee0717dbcf0c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (Edge Security)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cvent</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6178f1c0d02f2ef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cvent</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1c1fe22ded8d905</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (Edge Security)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cvent</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tysons Corner, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=331b84ff6903d8a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb2864d99d2cc3e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, Python, R, Java, C++, Julia, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcbceb6879bc1269</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c06ccb343ed594a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Database Research Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, C++, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c2c7ae28fcd3ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Asylon</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Norristown, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8a1286d2f88fa4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Java - Neovest</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pleasant Grove, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=696a17a7192f1333</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21db607c26bdabab</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a83fbcc49613465</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adcce0477cefa39a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=844146a4913a2f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45474185c720b04e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f729d01d886a8fe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65842d2a201780bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01bae81e33c2e463</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40aa2fef3287416d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12c0cdb238d6a988</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Appian Platform</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e61809c420b8c629</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Engineer 4 (AI Foundations: Benchmarking, Evaluation, and Explainability)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c07687fc8470a54</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-02.xlsx
+++ b/daily_matches/job_matches_2026-10-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca95058df9983f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f961336e7020a319</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VedaPointe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Redshift, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,59 +519,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67b03e4a412a6</t>
+          <t>https://www.indeed.com/viewjob?jk=393b88fa8c0cfa99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Production Bioinformatics Engineer</t>
+          <t>Sr. SW AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1c2a1b4ab40cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4c5148b3f23bba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Production Bioinformatics Engineer</t>
+          <t>Senior Data Scientist, Full Stack - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,42 +579,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2795ba2ac2c023</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd8af7bdf661443</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Snowflake, Hadoop, MongoDB, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, scikit-learn, S3, Databricks, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
+          <t>https://www.indeed.com/viewjob?jk=f69508452f9349a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Copy of Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Snowflake, Hadoop, MongoDB, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,312 +659,312 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c73622306892de8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Database and Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, RAG, Copilot, Synapse, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
+          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Applications</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RTI International</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, BigQuery, Git, BigQuery, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53c1a4e4aacfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=09fc26e8561c2d9b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (PySpark)</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PySpark, NoSQL, Python, SQL</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5576f999a81177b2</t>
+          <t>https://www.indeed.com/viewjob?jk=cce36fe2a3cc9555</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Shelton - Infrastructure - Engr- Dev Ops II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b2ab923ca77b28</t>
+          <t>https://www.indeed.com/viewjob?jk=961257a24d18a771</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Java, AWS)</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464c9249b43d0e07</t>
+          <t>https://www.indeed.com/viewjob?jk=8b55044556bd3f39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Specialist, Data Analysis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, Keras, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ced4fe47a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a111d7a7e205ddd3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Global Payment Network)</t>
+          <t>Sr. Full Stack Engineer I (6860)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Metrostar Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, Kubernetes, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1979d7025fe17b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=53f58a69bea46ca3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Cloud &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bunzl</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63f85728fde97d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3c303d5cb3d5a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer Intern - Property Management Data &amp; AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>SCG America Group Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, LLaMA, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f8927daa68bfadc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf7ee4dd283eeb2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Developer (AI, Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Allegheny County Pennsylvania</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,847 +1009,77 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa1ce1bef3bca57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>DynamoDB Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, Terraform, Git, MySQL, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2a448779a34adf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>DynamoDB Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, Terraform, Git, MySQL, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Associate Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=938793961653bac4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cvent</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ee0717dbcf0c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (Edge Security)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Cvent</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6178f1c0d02f2ef6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cvent</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c1fe22ded8d905</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (Edge Security)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cvent</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tysons Corner, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=331b84ff6903d8a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2864d99d2cc3e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PitchBook</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c06ccb343ed594a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Database Research Scientist</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>clickhouse</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MySQL, Python, SQL, R, C++, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2c7ae28fcd3ab1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Asylon</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Norristown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a1286d2f88fa4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Java - Neovest</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Pleasant Grove, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=696a17a7192f1333</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21db607c26bdabab</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a83fbcc49613465</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adcce0477cefa39a</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=844146a4913a2f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45474185c720b04e</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f729d01d886a8fe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65842d2a201780bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01bae81e33c2e463</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40aa2fef3287416d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12c0cdb238d6a988</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Appian Platform</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e61809c420b8c629</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI Engineer 4 (AI Foundations: Benchmarking, Evaluation, and Explainability)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c07687fc8470a54</t>
+          <t>https://www.indeed.com/viewjob?jk=46f074e4bc84ba37</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-02.xlsx
+++ b/daily_matches/job_matches_2026-10-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>CX Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, ChromaDB</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, scikit-learn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f961336e7020a319</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Pipeline Engineer</t>
+          <t>Senior Data Context Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VedaPointe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Redshift, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, S3, Glue, Athena, Redshift, Data Lake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393b88fa8c0cfa99</t>
+          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. SW AI Engineer</t>
+          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Glue, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4c5148b3f23bba</t>
+          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Full Stack - Remote</t>
+          <t>Applied AI Engineer (Full Stack AI Developer)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Kafka, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd8af7bdf661443</t>
+          <t>https://www.indeed.com/viewjob?jk=84ddffef7f5853db</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solutions Architect (Financial Services)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, scikit-learn, S3, Databricks, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69508452f9349a4</t>
+          <t>https://www.indeed.com/viewjob?jk=378fe0400293a18c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Copy of Snowflake Data Engineer</t>
+          <t>Data Analytics Specialist Sr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lutz, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Copilot, AKS, Git, Snowflake, Databricks, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c73622306892de8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Database and Platform Engineer</t>
+          <t>Senior Data Scientist (66_2026.3)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa904008bed68f6a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Sr. DevOps Engineer (FedRamp)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Black Duck Software</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, BigQuery, Git, BigQuery, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09fc26e8561c2d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=35bf791d87f5c796</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Senior Full-Stack Qlik Sense Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, Gemini, Data Lake, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce36fe2a3cc9555</t>
+          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shelton - Infrastructure - Engr- Dev Ops II</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Kubernetes, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961257a24d18a771</t>
+          <t>https://www.indeed.com/viewjob?jk=709b52a054edcae6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Senior Data Engineer - Indiana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Redshift, Git, Databricks, Redshift, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b55044556bd3f39</t>
+          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Specialist, Data Analysis</t>
+          <t>Data Engineer II - Zelle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, Keras, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Git, PySpark, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a111d7a7e205ddd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2de6c389d68d3fd0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer I (6860)</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metrostar Systems</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, Kubernetes, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, FastAPI, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f58a69bea46ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=7bfb1f315e35a1e5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Platform Engineer</t>
+          <t>Junior Data and AI-ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bunzl</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Data Lake, Databricks, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3c303d5cb3d5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=29f22521f3c1e203</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer Intern - Property Management Data &amp; AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCG America Group Inc.</t>
+          <t>FIT Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, BigQuery, Data Lake, AKS, BigQuery, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf7ee4dd283eeb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ede2763797092481</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allegheny County Pennsylvania</t>
+          <t>Nestlé USA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, Snowflake, Databricks, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa1ce1bef3bca57</t>
+          <t>https://www.indeed.com/viewjob?jk=2db6fee843320ce9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DynamoDB Engineer</t>
+          <t>Senior QA Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>ONENERGY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Git, MySQL, NoSQL, Python, SQL, R, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,42 +1044,952 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2a448779a34adf</t>
+          <t>https://www.indeed.com/viewjob?jk=69b5c19120976885</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DynamoDB Engineer</t>
+          <t>QE Automation Architect – Playwright / AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>FalconSmartIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94b12401c462b4ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e25df245e8dda5d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist (Forecasting)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nestlé USA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95d96574456a9f30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Anthony &amp; Sylvan Pools</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Warminster, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f2db93048d5792a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OneMagnify</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09997c9a80e4529c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, S3, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1535210094e76fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, S3, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=064cf120cd86f31c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Conversational AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, S3, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82f71d10a3b6b05d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Warehouse Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Copilot, Cortex, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cloud DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de84f98b95f16255</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Kubernetes</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0740a92bf27e943e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Victra-Verizon Authorized Retailer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31252c778ccd51aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b26364026b0bc1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6537378b4dc431c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Perception</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pickle Robot Company</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Charlestown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, PyTorch, YOLO, S3, EC2, Docker, Python, R, C++, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd79bb5e83636c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Agent Engineer, Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Orbis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ada02485dabac55</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Agent Engineer, Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ORBIS SE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e28118e75761521a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d8460c5dd6d8e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Core Team - San Jose, CA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ZEDEDA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Git, MySQL, NoSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46f074e4bc84ba37</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LangChain, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b584b897b6037e48</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Full-Stack Engineer (Laravel and Generative AI)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bake More Pies</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, AKS, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3162c3dd72fa4bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Perception Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lightspeed</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Northbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, OpenCV, Docker, CI/CD, Git, Python, R, C++</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12156177523019b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer — Backend (Files Team)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, Databricks, R, Java, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4e35258b086d99e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Billing)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bandwidth</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b955092352db74e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Architect - Indiana</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RadCube</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Git, Databricks, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9963d3eedaca5e2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - New Verticals Agentic Foundations</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab1bdd77f7c3f2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c45783565fb27c0</t>
         </is>
       </c>
     </row>
